--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1755,6 +1755,115 @@
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Abrate &amp; Sons Ltd</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Abrate &amp; Sons Ltd</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7499</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65 Wong Chuk Hang Road, Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://abrate.com</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>info@abrate.com</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>+852 2217 0006</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>21079248-000</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/abrate-and-sons/</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/abrateandsons/</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/abrate_and_sons/</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Mosun Abrate</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mosun-abrate-4617a413/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1864,6 +1864,220 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>The Juicy Grape Limited</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>The Juicy Grape Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7718</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Young Ya Industrial Building, 381-389 Sha Tsui Road, Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thejuicygrape.com</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>petertong@thejuicygrape.com</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>+852 3591 1345</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>63475775-000</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thejuicygrapelimited/</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thejuicygrapeltd/</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Peter Tong</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Founder - Director</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-tong-04938735/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Abrate &amp; Sons Ltd</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Abrate &amp; Sons Ltd</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7499</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>65 Wong Chuk Hang Road, Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://abrate.com</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>info@abrate.com</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>+852 2217 0006</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>21079248-000</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/abrate-and-sons/</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/abrateandsons/</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/abrate_and_sons/</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Mosun Abrate</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mosun-abrate-4617a413/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2078,321 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Alarcon Enterprise Limited</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Alarcon Enterprise Limited</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>119544</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Po Lung Centre, 11 Wang Chiu Road, Kowloon Bay</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>http://alarconenterprise.com</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>teresa@alarconenterprise.com</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>+852 3102 1383</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>64590871-000</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alarconenterprise/</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alarcon_enterprise/</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Teresa Chiu</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>The Juicy Grape Limited</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>The Juicy Grape Limited</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>7718</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Young Ya Industrial Building, 381-389 Sha Tsui Road, Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thejuicygrape.com</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>petertong@thejuicygrape.com</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>+852 3591 1345</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>63475775-000</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thejuicygrapelimited/</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thejuicygrapeltd/</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Peter Tong</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Founder - Director</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-tong-04938735/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Abrate &amp; Sons Ltd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Abrate &amp; Sons Ltd</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>7499</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>65 Wong Chuk Hang Road, Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://abrate.com</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>info@abrate.com</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>+852 2217 0006</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>21079248-000</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/abrate-and-sons/</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/abrateandsons/</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/abrate_and_sons/</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Mosun Abrate</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mosun-abrate-4617a413/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2393,6 +2393,321 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Alarcon Enterprise Limited</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Alarcon Enterprise Limited</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>119544</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Po Lung Centre, 11 Wang Chiu Road, Kowloon Bay</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>http://alarconenterprise.com</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>teresa@alarconenterprise.com</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>+852 3102 1383</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>64590871-000</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alarconenterprise/</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alarcon_enterprise/</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Teresa Chiu</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>The Juicy Grape Limited</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>The Juicy Grape Limited</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>7718</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Young Ya Industrial Building, 381-389 Sha Tsui Road, Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thejuicygrape.com</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>petertong@thejuicygrape.com</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>+852 3591 1345</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>63475775-000</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thejuicygrapelimited/</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thejuicygrapeltd/</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Peter Tong</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Founder - Director</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-tong-04938735/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Abrate &amp; Sons Ltd</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Abrate &amp; Sons Ltd</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>7499</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>65 Wong Chuk Hang Road, Wong Chuk Hang</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://abrate.com</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>info@abrate.com</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>+852 2217 0006</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>21079248-000</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/abrate-and-sons/</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/abrateandsons/</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/abrate_and_sons/</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Mosun Abrate</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mosun-abrate-4617a413/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2708,6 +2708,1971 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT WINES LIMITED</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Laithwaites Wine</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>167926</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3/F E-Commerce Logistics Ctr</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.directwines.com.hk</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5806576</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>customerservicehk@directwinesasia.com</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>50411798-000</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/directwineshk/</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/directwineshk/</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>SIMON NAI-CHENG HSU</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT WINES LIMITED</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Laithwaites Wine</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>167926</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3/F E-Commerce Logistics Ctr</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.directwines.com.hk</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5806576</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>customerservicehk@directwinesasia.com</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>50411798-000</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/directwineshk/</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/directwineshk/</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>YUEN CHUEN NG</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT WINES LIMITED</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Laithwaites Wine</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>167926</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3/F E-Commerce Logistics Ctr</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.directwines.com.hk</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5806576</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>customerservicehk@directwinesasia.com</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>50411798-000</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/directwineshk/</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/directwineshk/</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>CHI HUSAN LIU</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Vinosophy Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>167925</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Causeway Bay</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Rm 2457 LEE GDN ONE</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinosophy.hk</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>wine@vinosophy.hk</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>73693006-000</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinosophyhk/</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosophyhk/</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Pierre Legrandois</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>Founder/ Director</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/pierre-legrandois-14a18416</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Vinosophy Limited</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>167925</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Causeway Bay</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Rm 2457 LEE GDN ONE</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinosophy.hk</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>wine@vinosophy.hk</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>73693006-000</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinosophyhk/</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosophyhk/</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>James Kwan</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/james-kwan-dipwset</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>World Wine Exchange Limited</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>167924</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Tsim Sha Tsui</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Rm 1010 10/F SILVERCORD TWR 1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://worldwinehk.com</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>293724</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Winewec11@gmail.com</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>+852 6760 5611</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>74973154-000</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wwineofficial/</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Yu Fan Sung</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Well Sharp Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>167923</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Rm D 11/F EFFORT INDL BLDG</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineoptionhk.com</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>50861</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>services@wineoptionhk.com</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>67738195-000</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61566404176494</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineoptionhk/</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>Chi Wing Wong</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BAKUS CELLARS LIMITED</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>167921</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Rm 2205 22/F TSUEN WAN INDL CTR</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://bakuscellars.hk</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>116058</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>sales@bakuscellars.hk</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>+852 6058 8002</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>72485084-000</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bakus.cellars</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Christophe Denis Pierre E Castellino</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CHEUNG KEE INTERNATIONAL HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>167920</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Tai Po</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>G/F</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://cheungkeews.com</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>50861</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>waisun2003@gmail.com</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>+852 2650 8528</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>37918042-000</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wsguide/</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Wai Sun Master Lam</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>WINE ONLY</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>167919</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Tsing Yi Island</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Rm C 8/F GRAND HORIZON BLK 2</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://wineonly.store</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>196756</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>info@wineonly.store</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>41186209-000</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineonlyhk/</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineonlyhk/</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Wai Kiu Lo</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Great Resources International Group Limited</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>167916</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Fan Ling</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Rm C 8/F HI-SPEED CTR I</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greatresources.net</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>391632</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>info@greatresources.net</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>+852 3702 0199</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>64573043-000</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Ming Hung Iu</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Someone's Wine Limited</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>167914</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tsim Sha Tsui</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Shop G46, 67 Mody Rd</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://someoneswine.store</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>33907</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>someoneswineshop@gmail.com</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>70579409-000</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100064068400130</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/someones_wine_shop/</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Ping Sum Chong</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Vero Concept Limited</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>167913</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Central District</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Rm 701 7/F EURO TRADE CTR</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.veroconcept.com.hk</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>688916</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>marketing@veroconcept.com.hk</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>63968429-000</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veroconcepthk/</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veroconcept/</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>ESTHER LEE</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/estherlee-hk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HOP HING LOONG COMPANY, LIMITED</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>167910</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Sha Tin</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>3/F Veristrong Indl Ctr Blk A</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hhlstore.com</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>984165</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>enquiry@hophingloong.com.hk</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>+852 2271 8785</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>03753199-000</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/HHLhongkong</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hhlstorewinesake</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Randy Lee</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/randy-lee-6b706740/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HOP HING LOONG COMPANY, LIMITED</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>167910</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Sha Tin</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3/F Veristrong Indl Ctr Blk A</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hhlstore.com</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>984165</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>enquiry@hophingloong.com.hk</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>+852 2271 8785</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>03753199-000</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/HHLhongkong</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hhlstorewinesake</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Eric Lin</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eric-lin-8675a064/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ACKER MERRALL &amp; CONDIT (ASIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>167909</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Town</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>3/F China Merchants Godown B</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://hk.ackerwines.com</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>203443</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>info@ackerasia.com</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>+852 2525 0538</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>38917403-000</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/acker-merrall-&amp;-condit/</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AckerWines/</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ackerwines/</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/AckerMerrall</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCuQdyQt1o0wBLe4dvlWKVxg</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Ken Hui</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>Head of Wine Merchant Business, Asia</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/ken-hui-659a37a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ELEGANT FINE WINE (H.K.) LIMITED</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>167908</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Rm 607-608 6/F PROSPERITY CTR</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://efwhk.com</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3189358</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@efwhk.com</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>+852 2388 4880</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>69405615-000</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EFWHK-184948395525030</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/efwhk</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCUIq9FJbb_xaQpbTQWVY3IA/featured</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Kirsty Wong</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Operation Manager</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ELEGANT FINE WINE (H.K.) LIMITED</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>167908</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Rm 607-608 6/F PROSPERITY CTR</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://efwhk.com</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3189358</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@efwhk.com</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>+852 2388 4880</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>69405615-000</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EFWHK-184948395525030</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/efwhk</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCUIq9FJbb_xaQpbTQWVY3IA/featured</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Li</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ELEGANT FINE WINE (H.K.) LIMITED</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>167908</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Rm 607-608 6/F PROSPERITY CTR</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://efwhk.com</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3189358</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@efwhk.com</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>+852 2388 4880</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>69405615-000</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EFWHK-184948395525030</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/efwhk</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCUIq9FJbb_xaQpbTQWVY3IA/featured</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>HIU NAM LI</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ELEGANT FINE WINE (H.K.) LIMITED</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>167908</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Rm 607-608 6/F PROSPERITY CTR</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://efwhk.com</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3189358</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@efwhk.com</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>+852 2388 4880</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>69405615-000</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EFWHK-184948395525030</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/efwhk</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCUIq9FJbb_xaQpbTQWVY3IA/featured</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Jimmy Au</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ELEGANT FINE WINE (H.K.) LIMITED</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>167908</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Rm 607-608 6/F PROSPERITY CTR</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://efwhk.com</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3189358</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>inquiry@efwhk.com</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>+852 2388 4880</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>69405615-000</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EFWHK-184948395525030</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/efwhk</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCUIq9FJbb_xaQpbTQWVY3IA/featured</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>Alfred Liang</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4673,6 +4673,665 @@
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>FINE WINE RESERVE LIMITED</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>167937</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Causeway Bay</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Rm A 19/F CHINAWEAL CTR</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://fwr.asia</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>203443</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>contact@fwr.asia</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>+852 2572 0990</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>75651761-000</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/finewinereserve</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/finewinereservehk</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Denis Maurice Georges Martinet</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CHEONG HING (1917) LIMITED</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CHEONG HING VINSAC</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>167933</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Tsim Sha Tsui East</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Rm 911 9/F NEW MANDARIN PLZ TWR B</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cheong-hing.com</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>118675</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>cs@cheong-hing.com</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>+852 2687 5879</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>07721184-000</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ZwillingHK</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Tsui</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>Sales Attendant</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/dominic-tsui-556b03223</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Alcohood Limited</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>167931</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Rm 804-5 8/F MEGA TRADE CTR</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://alcohood.com</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>787332</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>info@alcohood.com</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>72424234-000</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/alcohood-ltd/</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alcohoodhk</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alcohoodhk/</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCkHcfj3pNJMFeWDYI8cP5AA/featured</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Billy Ng</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/billy-ng</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GDV Fine Wines</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>167929</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Wan Chai</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Rm B1 G/F</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gdv.com.hk</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>881172</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>vip@gdv.com.hk</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>21003128-000</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gdvfinewines/</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gdv.finewines/</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gdvfinewines/</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Paul Yeung</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/paul-yeung-dipwset-wset-certified-educator-22269a</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GDV Fine Wines</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>167929</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Wan Chai</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Rm B1 G/F</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gdv.com.hk</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>881172</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>vip@gdv.com.hk</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>21003128-000</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gdvfinewines/</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gdv.finewines/</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gdvfinewines/</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Jacky Lam</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing Senior Officer</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jacky-lam-048021bb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Anrise-imc Limited</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Anrise-imc Limited</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>7516</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Wong's Factory Building, 368-370 Sha Tsui Road, Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>http://anriseimc.com</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>info@anriseimc.com</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>+852 2573 8782</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>Alan Chiu</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>https://hk.linkedin.com/in/alanphchiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Chateau Cru Wine Limited</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Chateau Cru Wine Limited</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>7847</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>491-501 Castle Peak Road</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chateaucru.com.hk</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>sales@chateaucru.com.hk</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>+852 3590 6273</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>39170933-000</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>Alfred She</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alfred-she-41123834/?originalSubdomain=hk</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA50"/>
+  <dimension ref="A1:AA75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5332,6 +5332,2171 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>BEAQUA WINES AND SPIRITS COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>168269</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon City</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Lg 08/F Kowloon City Plz</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://beaquahk.com</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>33907</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>info@beaquahk.com</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>71567366-000</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beaquahk/</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr"/>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Innotaste GmbH</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>168245</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Sha Tin</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Rm D 2/F ON WAH INDL BLDG</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://innotaste.com</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>293944</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>csila@innotaste.com</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>+49 2151 525470</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>73209968-000</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/innotaste/</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Schockhoven</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/andreasschockhoven</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Innotaste GmbH</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>168245</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Sha Tin</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Rm D 2/F ON WAH INDL BLDG</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>https://innotaste.com</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>293944</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>csila@innotaste.com</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>+49 2151 525470</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>73209968-000</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/innotaste/</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>Sophie Marie Karayusuf</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Specialist</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sophie-marie-karayusuf-503838203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Innotaste GmbH</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>168245</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Sha Tin</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Rm D 2/F ON WAH INDL BLDG</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://innotaste.com</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>293944</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>csila@innotaste.com</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>+49 2151 525470</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>73209968-000</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/innotaste/</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>Claudia Sila</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/claudia-sila-04790b276</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>THE WINE GUILD HK LIMITED</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>168244</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Central District</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Rm 5 G/F RYAN MANSION</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://hkwineguild.com</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>50861</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>jb@hkwineguild.com</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>68220446-000</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hkwineguild/</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hkwineguild</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hkwineguild/</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Baptiste Mage</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jean-baptiste-mage-95703115/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>THE WINE GUILD HK LIMITED</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>168244</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Central District</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Rm 5 G/F RYAN MANSION</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://hkwineguild.com</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>50861</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>jb@hkwineguild.com</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>68220446-000</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hkwineguild/</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hkwineguild</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hkwineguild/</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>Valentin Larose</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager and Marketing Coordinator</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/valentin-larose</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>M WINES LIMITED</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>MING WINES</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>168243</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Central District</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Rm D 10/F HO LEE COML BLDG</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://mingwines.com</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>232115</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>info@mingwines.com</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>+852 2810 1808</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>69472286-000</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr"/>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>PROVINERY LIMITED</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>168241</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Rm 1503 ENTREPOT CTR</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://provinery.com</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>hugo@provinery.com</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>75558876-000</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-provinery/</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theprovinery?igsh=MTJvdnNpdWI2NzB5aQ==</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@theprovinery</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>Marie Haddad</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/haddad-marie</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Solomon Vintners Limited</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>168240</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Central District</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Rm 2007 20/F LKF TWR</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://solomonvintners.com</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>info@solomonvintners.com</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>73814565-000</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solomon-vintners/</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solomonvintnershk/</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>Rosanna A.</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rosanna-a-47270048/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Solomon Vintners Limited</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>168240</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Central District</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Rm 2007 20/F LKF TWR</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://solomonvintners.com</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>info@solomonvintners.com</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>73814565-000</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solomon-vintners/</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solomonvintnershk/</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>Sally Wong</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sallyttw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Sippin HK Limited</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>168239</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Sai Ying Pun</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Room 3304, 33/F, Cheng Kei Commercial Centre, 144-151 Connaught Road West</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://sippinhk.com</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>sales@sippinhk.com</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>73914850-000</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sippinhk</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sippin.hk/</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr"/>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>The Missing Bottle Limited</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>168234</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Rm 2004-06 20/F STRAND 50</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://themissingbottle.com</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>info@themissingbottle.com</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>72840365-000</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-missing-bottle/about/</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/themissingbottle?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>Megan Lui</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/megan-lui-6a89879a</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>The Missing Bottle Limited</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>168234</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Rm 2004-06 20/F STRAND 50</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://themissingbottle.com</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>info@themissingbottle.com</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>72840365-000</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-missing-bottle/about/</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/themissingbottle?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>Aurélien Guédès</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director &amp; Founder</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aurelienguedes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>The Vine Gallery Limited</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>168233</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Wan Chai</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>G/F Nam Shing Bldg</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://thevine-gallery.com</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>203443</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>info@thevine-gallery.com</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>72873451-000</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>Jumpei Tanaka</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Vinternet International Trading Co., Limited</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>168232</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Wan Chai</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Rm 903C 9/F CAMERON COML CTR</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://vinternet.com.hk</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5806576</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>support@vinternet.com.hk</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>65659541-000</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/vinternethk</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr"/>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>WINETALE FAR EAST LIMITED</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>168231</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Central District</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>5/F Far East Consortium Bldg</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://winetalefareastlimited.com</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>193430</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>info@winetalefareastlimited.com</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>61030260-000</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Kwok Fai Chan</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomas-kwok-fai-chan-7aba7018/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>BUND FINE WINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>168230</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon Bay</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Rm 7 9/F ENTERPRISE SQ THREE</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bundwines.com</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>984165</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>philippehuser@bundwines.com</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>60636576-000</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Huser</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>BUND FINE WINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>168230</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon Bay</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Rm 7 9/F ENTERPRISE SQ THREE</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bundwines.com</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>984165</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>philippehuser@bundwines.com</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>60636576-000</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>Maxime Gibrat</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxime-gibrat-0bba737/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>CCF Wines Limited</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>168228</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>North Point</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Rm 1607 16/F KODAK HSE</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ccfwines.com</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>688916</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>sales@ccfwines.com</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>+852 2880 7128</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>61893385-000</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr"/>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Kylix Limited</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>168226</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Rm 32 16/F WONG KING INDL BLDG BLK E</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kylixhk.com</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>84768</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>info@kylixhk.com</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>58210542-000</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kylixkitchen</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kylixkitchen/</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr"/>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>KP Wine Limited</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>168225</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Rm F1 16/F SHUI SUM INDL BLDG</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kp-wine.com</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>295250</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>info@kp-wine.com</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>+852 3468 5190</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>71836105-000</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>http://facebook.com/ECK-International-Trading-Limited-1944935282200802</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/kpwine_?igshid=NTc4MTIwNjQ2YQ==</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr"/>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>LA VIGNA LIMITED</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>168224</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>San Po Kong</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Rm 1020 NEW TECH PLZ</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lavigna.hk</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>84768</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>simon@lavigna.hk</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>+852 2626 1996</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>63030717-000</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>Simon Cheung</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simon-cheung-08104971/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>HEATFIRE1000</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>168223</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Rm B6 4/F CAMEL PAINT Bldg 1</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.heatfire1000.com</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>293029</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>heatfire1000@yahoo.com</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>50378827-000</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Lau</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-lau-b80a9630/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>96276</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Room 01, 10/f, Kowloon Plaza</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://mugigawa.com</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>info@mugigawa.com</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mugigawa</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mugi.liquor.jp</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr"/>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>37916</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Town</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Hing Industrial Building, 12P Smithfield, Kennedy Town</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://winemoments.com</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>hello@winemoments.com</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>+852 2111 9291</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>62681581-000</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winemomentshk</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Katy Murphy</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katymmurphy/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA75"/>
+  <dimension ref="A1:AA96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7497,6 +7497,1443 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Fine Wine Exchange</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>168373</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Tsim Sha Tsui</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Shop 191-202 1/F NEW MANDARIN PLAZA 14 SCIENCE MUSEUM RD</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://hkfinewine.com</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>info@hkfwec.com</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr"/>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Good Wine Limited </t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>168372</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1302B Wing Fung Industrial Building Sha Tsui Road</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.goodwinehk.com</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>sales@goodwinehk.com</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr"/>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Garuda Wines</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>168371</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Tsim Sha Tsui</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Unit 915, 9/F., Concordia Plaza 1 Science Museum Road</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://garudawines.hk</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>info@garudawines.hk</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr"/>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>iEverydayWine</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>168370</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Fo Tan</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Room 1306, Global Industrial Centre, Sanwei Street</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://ieverydaywine.com</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>cs@ieverydaywine.com</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>+852 2688 7506</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EverydaywineHK</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/ieverydaywinehk/</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr"/>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Wine Cloud</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>168369</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Suite 12, 22/F, Wayson Commercial Building, 28 Connaught Road West</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://winecloud.hk</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>hello@winecloud.hk</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/Wine-Cloud-HK-112862201432888</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/winecloudhk</t>
+        </is>
+      </c>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr"/>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Leighton Wine</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>168368</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Happy Valley</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>G/F, Broadview Mansion, 73D, Wong Nai Chung Road</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.leightonwine.com</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>leightonwine87@gmail.com</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LeightonWine/</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/leighton_wine/</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>Lin Shuting</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%E8%88%92%E5%A9%B7-%E6%9E%97-7382ab226/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Silene Wine Shop</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>168367</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>G/F &amp; LG/F, 33 Aberdeen Street</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.silenewineshop.com</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>hello@silenewinebar.com</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>+852 2885 9599</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61571110907931</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/silenewineshop</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="2" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr"/>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Joy Union International Trading Limited</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>168366</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Sha Tin</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>10-16 Wo Shing Street, Hoi Fai Industrial Centre, Room 1107</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://joyunion.hk</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>sales@joyunion.hk</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>+852 2116 5322</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr"/>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>World of Wines Company Limited</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>168365</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Unit 4B, 4/F Kapok Industrial Building 373 To Kwa Wan Road</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://wowshk.com</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Info@wowshk.com</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>+852 2559 1998</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr"/>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>K Group Wine</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>168364</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Room B11, 1/F, Yip Win Industrial Building, 10 Tsun Yip Lane</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kgroupwine.com</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>kgroupwine@yahoo.com.hk</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063726834063</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kgroupwine/</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr"/>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Into the Vines</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>168363</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>16 Argyle Street, Mongkok Commercial Center, Unit 2104, 21/F.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://intothevines.hk</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>contact@intothevines.hk</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/winetastic.hk/</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr"/>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>L'Imperatrice Fine Wines</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>168362</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Room 404-406 4/F, Hollywood Centre, 233 Hollywood Road</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>info@imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imperatrice-hong-kong/</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>Jeanne Jobard</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Executive</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jeanne-jobard-b4aa3599</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>L'Imperatrice Fine Wines</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>168362</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Room 404-406 4/F, Hollywood Centre, 233 Hollywood Road</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>info@imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imperatrice-hong-kong/</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>Jessica Chan</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>Food and Beverage Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jessica-o-l-chan-a3232526</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>L'Imperatrice Fine Wines</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>168362</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Room 404-406 4/F, Hollywood Centre, 233 Hollywood Road</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>info@imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imperatrice-hong-kong/</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>Stephane Phaseuth</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>Private Sales</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/stephane-phaseuth-023259172</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>L'Imperatrice Fine Wines</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>168362</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Room 404-406 4/F, Hollywood Centre, 233 Hollywood Road</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>info@imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imperatrice-hong-kong/</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>Sunny Wong</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>Sales Account Manager</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/sunny-wong-1babb498</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>L'Imperatrice Fine Wines</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>168362</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Room 404-406 4/F, Hollywood Centre, 233 Hollywood Road</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>info@imperatrice.com.hk</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imperatrice-hong-kong/</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>F Hirsch</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>Sales and Marketing Director</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/f-hirsch-b627b532</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>HK Wine Forest</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>168361</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Room 2315, 23/F, North Tower, Concord Plaza</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://hkwineforest.com</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>hkwineforest@gmail.com</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr"/>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>La Souveraine Fine Wine</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>168360</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Sheung Wan</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>14 Wa In Fong East</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>https://souverainewine.com</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>julien@souverainewine.com</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/souverainewine</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/souverainewine/</t>
+        </is>
+      </c>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr"/>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Wine O'Cork</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>168359</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Wan Chai</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Room 2007, 20th Floor, 382 Lockhart Road</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineocork.com</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>info@wineocork.com</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine.o.cork/</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr"/>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>96276</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Room 01, 10/f, Kowloon Plaza</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>https://mugigawa.com</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>info@mugigawa.com</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mugigawa</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mugi.liquor.jp</t>
+        </is>
+      </c>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr"/>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>37916</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Town</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Hing Industrial Building, 12P Smithfield, Kennedy Town</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://winemoments.com</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>hello@winemoments.com</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>+852 2111 9291</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>62681581-000</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winemomentshk</t>
+        </is>
+      </c>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>Katy Murphy</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katymmurphy/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA96"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8934,6 +8934,2181 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>T'z Limited</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>168401</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Quarry Bay</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1807, 18/F, Eastern Harbour Centre, No. 28 Hoi Chak Street</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tzgroup.com.hk</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>tz@tzgroup.com.hk</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>+852 2310 0889</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Tz-Limited-100063911509100/</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tz_limited/</t>
+        </is>
+      </c>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>Peggy Tse</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peggy-tse-6b14bb120/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Berry Bros. &amp; Rudd Hong Kong</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>168400</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>80 Queen's Road Central</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://bbr.com.hk</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>hkenquiries@bbr.com</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>+852 2511 2811</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr"/>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Boho Club</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>168399</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Admiralty</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>16 Harcourt Road, Far East Finance Centre, UG Tower, Unit A5-3</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bohoclub.com.hk</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>info@bohoclub.com.hk</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bohoclubhk</t>
+        </is>
+      </c>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr"/>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treasures Wine </t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>168398</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Chai Wan</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Room 807B, 8/F, Cornell Centre, 50 Wing Tai Road</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://treasureswine.com</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>info@treasureswine.com</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr"/>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Strong Harbour Ltd</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>168397</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Yau Tong</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>428 Cha Kwo Ling Road</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.strongharbour.com</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>info@strongharbour.com</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>+852 2544 6433</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr"/>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Swallowking Liquor</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>168396</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Chai Wan</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Flat 1007-1008, Cheung Tat Centre, 18 Cheung Lee Street</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.swallowkingliquor.com</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>swallowkingliquor@gmail.com</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/swallowkingliquorr/</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/swallowking_liquor/</t>
+        </is>
+      </c>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr"/>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Wine Horsemen</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>168395</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Room 1601, 16/F, Silvercord Tower 2, 30 Canton Road, Tsim Sha Tsui</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winehorsemen.com</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>info@winehorsemen.com</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehorsemen</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehorsemen</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr"/>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Vino - Artisan Italian Wine</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>168394</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Sai Kung</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Che Keng Tuk</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>http://vino.com.hk</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>thirsty@vino.com.hk</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vino.com.hk</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>Henrietta Hutchings</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/henrietta-hutchings-04bb096/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>V Wine Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>168393</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Room 909, 9/F, Block A, Hi-tech Industrial Centre, 5-21 Pak Tin Par Street</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://vwinehk.com</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>hello@vwinehk.com</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vwinehk</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vwinehk/</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr"/>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Terroir &amp; Craft (天地人酒業)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>168392</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Room 509, 5/F, Seaview Centre, 139 Hoi Bun Road</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.terroirandcraft.online</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>eshop@terroirandcraft.com</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>+852 2981 8868</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr"/>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Booze By The Box</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>168391</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Sai Kung</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>G/F Man Yip Building, 52 See Cheung St</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boozebythebox.com.hk</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>hello@boozebythebox.com.hk</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boozebythebox/</t>
+        </is>
+      </c>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr"/>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Vino Conte (酒伯爵)</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>168390</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Fong</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>16-26 Kwai Tak Street</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinoconte.com</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>info@vinoconte.com</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>+852 2466 0311</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>Sharpe Law</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sharpelaw/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>VIVANT</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>168389</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>2/F, Welland House</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://vivanthk.com</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>info@vivanthk.com</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr"/>
+      <c r="X109" s="2" t="inlineStr"/>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Tai Yick Co. Ltd</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>168387</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Sai Kung</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>No. 19, Tin Liau Village, Ho Chung</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://drinks.com.hk</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>info@drinks.com.hk</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>+852 2345 1698</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr"/>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Wine Casa HK</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>168386</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>47 Hoi Yuen Road</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winecasahk.com</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>sales@winecasahk.com</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr"/>
+      <c r="X111" s="2" t="inlineStr"/>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Wine Time</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>168385</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Tsuen Wan</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>84-92 Chai Wan Kok Street</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>999077</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winetimehk.com</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>sales@winetimehk.com</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winetimecoltd</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine_time_hk/</t>
+        </is>
+      </c>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr"/>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>One Cellar Hong Kong Company Limited</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>168383</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Shop 3B, G/F, 44-46 Hung To Road</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://onecellarhongkong.com</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>info@onecellarhongkong.com</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>+852 3793 4095</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr"/>
+      <c r="R113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>Aaron Chung</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Managing Director </t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aaron-chung-15833ba3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Wine Library</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>168382</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Wan Chai</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>G/F, Shop 21 Lee Tung Street</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://winelibraryhk.com.hk</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>info@winelibraryhk.com.hk</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winelibraryhongkong</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winelibraryhk/</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr"/>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>A&amp;T (HK) Wines Ltd</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>168381</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Unit 8, 28/F, Clifford Centre, 778-784 Cheung Sha Wan Road</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atwines.com.hk</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>sales@atwines.com.hk</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr"/>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr"/>
+      <c r="X115" s="2" t="inlineStr"/>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Beverage World Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>168380</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Chai Wan</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>7 Cheung Lee Street, Man Foong Industrial Bld, 18 Floor, Room A</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr"/>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beverageworld.com.hk</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>sales@beverageworld.com.hk</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>+852 2838 5777</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61585096066981</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beverageworldhksar/</t>
+        </is>
+      </c>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr"/>
+      <c r="X116" s="2" t="inlineStr"/>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>PP Wine Cellar (小彭酒窖)</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>168379</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Causeway Bay</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Units A &amp; B, 6/F, KT Group Building, 18 Pennington Street</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ppwinecellar.com</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>info@ppwinecellar.com</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>+852 2808 0908</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr"/>
+      <c r="R117" s="2" t="inlineStr"/>
+      <c r="S117" s="2" t="inlineStr"/>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr"/>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Costa Wine Limited</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>168378</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Room 3, G/F, Hung Tat Ind. Building, 43 Hung To Road</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://costawinehk.com</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>costawineltd@gmail.com</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>+852 2357 0039</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr"/>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CostaWineLimited</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/costawineltd/</t>
+        </is>
+      </c>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr"/>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Diverxu Limited</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>168377</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Unit A, 7/F, Stage 2, Wah Fung Industrial Centre, 33-39 Kwai Fung Road</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.diverxu.com</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>info@diverxu.com</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>+852 3118 1676</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr"/>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Diverxu</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diverxu.hk/</t>
+        </is>
+      </c>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>Dorothy Lee</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>Accounts &amp; Admin Executive</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dorothy-lee-0a778353/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">French Wine Direct </t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>168376</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Sha Tin</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Room 1102, Block A, New World Centre, 6 On Ping Street</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>http://frenchwinedirect.com.hk</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>info@frenchwinedirect.com.hk</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>+852 2544 1438</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr"/>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/frenchwinedirect</t>
+        </is>
+      </c>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+      <c r="X120" s="2" t="inlineStr"/>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>HK Beverages &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>168375</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Unit B, 5th Floor, Che Wah Industrial Building. 1-7 Kin Hong Street</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://bevspirits.hk</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>hkbeveragespirits@gmail.com</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr"/>
+      <c r="R121" s="2" t="inlineStr"/>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61570840105337</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hkbeverages/</t>
+        </is>
+      </c>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+      <c r="X121" s="2" t="inlineStr"/>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Wine Ltd.</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>168374</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Shop 711, 7/F, Fortune Metropolis Shopping Mall, Hung Hom</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hongkongwine.com</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>channisli@hkwine.com.hk</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>+852 2383 0219</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr"/>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063757072387&amp;mibextid=ZbWKwL</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hk.wine/</t>
+        </is>
+      </c>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr"/>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr"/>
+      <c r="R123" s="2" t="inlineStr"/>
+      <c r="S123" s="2" t="inlineStr"/>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>Debby Yip</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>Deputy Director, Specialist, Head of Contemporary Day Auction</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/debby-yip-8a653b129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>Freddy C.</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>Senior Business Director</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/freddychi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr"/>
+      <c r="R125" s="2" t="inlineStr"/>
+      <c r="S125" s="2" t="inlineStr"/>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>Terrence Chim</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>Specialist, Wine Retail &amp; Private Sales</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/terrence-chim-1048a012a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>96276</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Room 01, 10/f, Kowloon Plaza</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://mugigawa.com</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>info@mugigawa.com</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr"/>
+      <c r="R126" s="2" t="inlineStr"/>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mugigawa</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mugi.liquor.jp</t>
+        </is>
+      </c>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
+      <c r="X126" s="2" t="inlineStr"/>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>37916</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Town</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Hing Industrial Building, 12P Smithfield, Kennedy Town</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://winemoments.com</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>hello@winemoments.com</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>+852 2111 9291</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>62681581-000</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr"/>
+      <c r="S127" s="2" t="inlineStr"/>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winemomentshk</t>
+        </is>
+      </c>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>Katy Murphy</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katymmurphy/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11109,6 +11109,407 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>Debby Yip</t>
+        </is>
+      </c>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>Deputy Director, Specialist, Head of Contemporary Day Auction</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/debby-yip-8a653b129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr"/>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr"/>
+      <c r="R129" s="2" t="inlineStr"/>
+      <c r="S129" s="2" t="inlineStr"/>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>Freddy C.</t>
+        </is>
+      </c>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>Senior Business Director</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/freddychi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr"/>
+      <c r="R130" s="2" t="inlineStr"/>
+      <c r="S130" s="2" t="inlineStr"/>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>Terrence Chim</t>
+        </is>
+      </c>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>Specialist, Wine Retail &amp; Private Sales</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/terrence-chim-1048a012a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>96276</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Room 01, 10/f, Kowloon Plaza</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://mugigawa.com</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>info@mugigawa.com</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr"/>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr"/>
+      <c r="R131" s="2" t="inlineStr"/>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mugigawa</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mugi.liquor.jp</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
+      <c r="X131" s="2" t="inlineStr"/>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>37916</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Town</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Hing Industrial Building, 12P Smithfield, Kennedy Town</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://winemoments.com</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>hello@winemoments.com</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>+852 2111 9291</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>62681581-000</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr"/>
+      <c r="S132" s="2" t="inlineStr"/>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winemomentshk</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>Katy Murphy</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katymmurphy/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA132"/>
+  <dimension ref="A1:AA137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11510,6 +11510,407 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr"/>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr"/>
+      <c r="R133" s="2" t="inlineStr"/>
+      <c r="S133" s="2" t="inlineStr"/>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>Debby Yip</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>Deputy Director, Specialist, Head of Contemporary Day Auction</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/debby-yip-8a653b129/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr"/>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="R134" s="2" t="inlineStr"/>
+      <c r="S134" s="2" t="inlineStr"/>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>Freddy C.</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>Senior Business Director</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/freddychi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Sotheby's Wine Hong Kong</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr"/>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>18568</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Shops G1-G2, G/F, Chater House 8 Connaught Road</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://wine.sothebys.com, https://www.sothebyswine.com</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>wineHK@sothebys.com</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>+852 2886 7888</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr"/>
+      <c r="R135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="inlineStr"/>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>Terrence Chim</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>Specialist, Wine Retail &amp; Private Sales</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/terrence-chim-1048a012a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Mugigawa</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>96276</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Sha Wan</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Kowloon</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Room 01, 10/f, Kowloon Plaza</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://mugigawa.com</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>info@mugigawa.com</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr"/>
+      <c r="R136" s="2" t="inlineStr"/>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mugigawa</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mugi.liquor.jp</t>
+        </is>
+      </c>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr"/>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Joyvino Limited</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>37916</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Town</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Cheung Hing Industrial Building, 12P Smithfield, Kennedy Town</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>https://winemoments.com</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>hello@winemoments.com</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>+852 2111 9291</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>62681581-000</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr"/>
+      <c r="S137" s="2" t="inlineStr"/>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winemomentshk</t>
+        </is>
+      </c>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>Katy Murphy</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katymmurphy/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
